--- a/artfynd/A 4916-2023 artfynd.xlsx
+++ b/artfynd/A 4916-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117745701</v>
+        <v>117746182</v>
       </c>
       <c r="B2" t="n">
-        <v>41164</v>
+        <v>100007</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100453</v>
+        <v>222771</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trolldruvemätare</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Baptria tibiale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Esper, 1790)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483161</v>
+        <v>483190</v>
       </c>
       <c r="R2" t="n">
-        <v>6997263</v>
+        <v>6997332</v>
       </c>
       <c r="S2" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117745191</v>
+        <v>117745049</v>
       </c>
       <c r="B3" t="n">
         <v>41164</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483131</v>
+        <v>483141</v>
       </c>
       <c r="R3" t="n">
-        <v>6997393</v>
+        <v>6997317</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117746182</v>
+        <v>117745701</v>
       </c>
       <c r="B4" t="n">
-        <v>100007</v>
+        <v>41164</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>100453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483190</v>
+        <v>483161</v>
       </c>
       <c r="R4" t="n">
-        <v>6997332</v>
+        <v>6997263</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117745049</v>
+        <v>117745191</v>
       </c>
       <c r="B5" t="n">
         <v>41164</v>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483141</v>
+        <v>483131</v>
       </c>
       <c r="R5" t="n">
-        <v>6997317</v>
+        <v>6997393</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 4916-2023 artfynd.xlsx
+++ b/artfynd/A 4916-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117746182</v>
+        <v>117745191</v>
       </c>
       <c r="B2" t="n">
-        <v>100007</v>
+        <v>41164</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>100453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483190</v>
+        <v>483131</v>
       </c>
       <c r="R2" t="n">
-        <v>6997332</v>
+        <v>6997393</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117745191</v>
+        <v>117746182</v>
       </c>
       <c r="B5" t="n">
-        <v>41164</v>
+        <v>100009</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100453</v>
+        <v>222771</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trolldruvemätare</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Baptria tibiale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Esper, 1790)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483131</v>
+        <v>483190</v>
       </c>
       <c r="R5" t="n">
-        <v>6997393</v>
+        <v>6997332</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 4916-2023 artfynd.xlsx
+++ b/artfynd/A 4916-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117745701</v>
+        <v>117745049</v>
       </c>
       <c r="B2" t="n">
-        <v>41164</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41670</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,17 +706,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bodflon (Bodflon), Jmt</t>
+          <t>Bodflon, Bodflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483161</v>
+        <v>483141</v>
       </c>
       <c r="R2" t="n">
-        <v>6997263</v>
+        <v>6997317</v>
       </c>
       <c r="S2" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -780,12 +775,7 @@
         <v>117745191</v>
       </c>
       <c r="B3" t="n">
-        <v>41164</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,7 +803,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bodflon (Bodflon), Jmt</t>
+          <t>Bodflon, Bodflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -879,53 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117746182</v>
+        <v>117745701</v>
       </c>
       <c r="B4" t="n">
-        <v>100011</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>100453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodflon (Bodflon), Jmt</t>
+          <t>Bodflon, Bodflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483190</v>
+        <v>483161</v>
       </c>
       <c r="R4" t="n">
-        <v>6997332</v>
+        <v>6997263</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,53 +966,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117745049</v>
+        <v>117746182</v>
       </c>
       <c r="B5" t="n">
-        <v>41164</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100453</v>
+        <v>222771</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trolldruvemätare</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Baptria tibiale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Esper, 1790)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodflon (Bodflon), Jmt</t>
+          <t>Bodflon, Bodflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483141</v>
+        <v>483190</v>
       </c>
       <c r="R5" t="n">
-        <v>6997317</v>
+        <v>6997332</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 4916-2023 artfynd.xlsx
+++ b/artfynd/A 4916-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117745049</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117745191</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117745701</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,8 +1080,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117746182</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>